--- a/data/trans_orig/IP13_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Edad-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (Tasa respuesta: 99,9%)</t>
+          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -667,70 +715,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3969</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>3255</v>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7485</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>5,3%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>7224</v>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>9081</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>53542</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>58189</v>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,53%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>212</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>111731</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5735</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>57511</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53542</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>49896</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>61444</v>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>96,61%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>58189</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>118955</v>
+          <t>53959</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>60252</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>111731</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>106831</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>115026</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>93,93%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>89,81%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>9081</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>57511</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>14470</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>23551</v>
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>243</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>150218</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7017</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>167360</v>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>494</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>317579</v>
+          <t>6871</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18383</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>18132</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>11883</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>24841</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>258</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>159299</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>494</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>275</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>181830</v>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>533</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>341130</v>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7441</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>5419</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>10549</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>150218</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>144397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>153937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>15688</v>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>251</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>167360</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>26237</v>
+          <t>159861</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>172475</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>317579</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>309243</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>324713</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>90,65%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>218</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>162523</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>159299</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>159299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>159299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>196802</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>275</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>181830</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>443</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>359326</v>
+          <t>181830</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>181830</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>341130</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>341130</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>341130</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>173072</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>243</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>212490</v>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>476</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>385563</v>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>17577</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>18927</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>11986</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>28567</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>13839</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2346</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>15004</v>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>28842</v>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10709</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>7310</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>13160</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>322</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>261619</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>162523</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>156226</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>323</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>290479</v>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>225</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>196802</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>645</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>552098</v>
+          <t>189055</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>202844</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>359326</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>348167</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>367115</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>90,3%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>342</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>275458</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173072</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>173072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>173072</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>342</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>305483</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>243</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>212490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>684</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>580940</v>
+          <t>212490</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>212490</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,6 +2040,36 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>385563</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>385563</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>385563</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1530,75 +2078,117 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>37437</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>48417</v>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>85854</v>
+          <t>6096</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>19247</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>21569</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>14322</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>29900</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1606,70 +2196,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>884</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>627903</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3729</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>910</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>712831</v>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1794</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>1340734</v>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9177</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>7274</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>3424</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>13528</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1677,75 +2309,686 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>942</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>665340</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>261619</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>253835</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>267398</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>761248</v>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>290479</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>1918</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>1426588</v>
+          <t>281505</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>296539</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>552098</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>541332</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>560799</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>95,04%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>93,18%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>275458</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>275458</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>275458</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>305483</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>305483</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>305483</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19011</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>36467</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>26271</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>47471</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>63411</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>51509</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>77482</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5914</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>16840</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>6848</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>19006</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>14731</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>31003</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>627903</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>617047</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>637527</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>95,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>712831</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>701590</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>724706</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1340734</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1324469</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1355278</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1426588</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1426588</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1426588</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1753,15 +2996,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP13_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>384</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49896</t>
+          <t>50091</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55563</t>
+          <t>55886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>53968</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106831</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115026</t>
+          <t>114885</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144397</t>
+          <t>144235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153937</t>
+          <t>154186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159861</t>
+          <t>160855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172475</t>
+          <t>172690</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>309243</t>
+          <t>309794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>324713</t>
+          <t>324302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156226</t>
+          <t>155882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167097</t>
+          <t>167028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189055</t>
+          <t>188319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202844</t>
+          <t>202628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348167</t>
+          <t>348492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367115</t>
+          <t>367366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17807</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253835</t>
+          <t>253885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>267398</t>
+          <t>267139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>281505</t>
+          <t>283117</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>296539</t>
+          <t>297003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>541332</t>
+          <t>541040</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>560799</t>
+          <t>560362</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>51166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77482</t>
+          <t>77859</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,47 +2682,47 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>6848</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>617047</t>
+          <t>618104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>637527</t>
+          <t>637340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>701590</t>
+          <t>699766</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>724706</t>
+          <t>723830</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1324469</t>
+          <t>1324144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1355278</t>
+          <t>1355038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6215</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1528</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3460</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5577</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47657</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>44322</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49505</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53542</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>50091</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55886</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58189</t>
+          <t>48596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53968</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60406</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>96253</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>91832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114885</t>
+          <t>99343</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9176</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14928</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11773</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6351</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>2064</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6245</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3355</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>423</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>145023</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>139150</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>149221</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>150218</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>144235</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>154186</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>167360</t>
+          <t>137208</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160855</t>
+          <t>131434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172690</t>
+          <t>140912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>317579</t>
+          <t>282230</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>309794</t>
+          <t>274843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>324302</t>
+          <t>287744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181830</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>302503</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,62 +1632,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10811</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6243</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,93%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8203</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4474</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14230</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>27093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10632</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2346</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6295</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>184342</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>176849</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>190441</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>162523</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>155882</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167028</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>164130</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188319</t>
+          <t>156941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202628</t>
+          <t>168357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>359326</t>
+          <t>348472</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348492</t>
+          <t>338223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367366</t>
+          <t>356305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3639</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8705</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>3729</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8555</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>277638</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>269125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>283894</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>322</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>261619</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>253885</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>267139</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>290479</t>
+          <t>242123</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>283117</t>
+          <t>234147</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>297003</t>
+          <t>247328</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>552098</t>
+          <t>519762</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>541040</t>
+          <t>509666</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>560362</t>
+          <t>528096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>34234</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>44933</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>18874</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>35042</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77859</t>
+          <t>74402</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>654660</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>641976</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>664532</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>884</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>627903</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>618104</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>637340</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>712831</t>
+          <t>592056</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>699766</t>
+          <t>581075</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>723830</t>
+          <t>600792</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1340734</t>
+          <t>1246716</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1324144</t>
+          <t>1229241</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1355038</t>
+          <t>1260932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
